--- a/InputData/elec/PMCRS/Pol Mandated Cap Retro Sched.xlsx
+++ b/InputData/elec/PMCRS/Pol Mandated Cap Retro Sched.xlsx
@@ -93468,4 +93468,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65B90A8E-4DEA-49F5-8E72-AD5B447E2775}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354982D4-7117-41F6-BFD4-E9FB39A896C4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74DD6AA2-F9C2-4570-B40A-EAF66B51B0D4}"/>
 </file>
--- a/InputData/elec/PMCRS/Pol Mandated Cap Retro Sched.xlsx
+++ b/InputData/elec/PMCRS/Pol Mandated Cap Retro Sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\PMCRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\elec\PMCRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD25105-A0D1-4B8F-9CCA-CFD230FDBD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7068686A-D7DF-471A-85CB-744CB49FA848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9199B2FD-BD64-4DD1-9285-C284D90C08CC}"/>
+    <workbookView xWindow="5835" yWindow="2625" windowWidth="31635" windowHeight="16815" activeTab="5" xr2:uid="{9199B2FD-BD64-4DD1-9285-C284D90C08CC}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -145,9 +145,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId7"/>
-    <pivotCache cacheId="4" r:id="rId8"/>
-    <pivotCache cacheId="5" r:id="rId9"/>
+    <pivotCache cacheId="12" r:id="rId7"/>
+    <pivotCache cacheId="13" r:id="rId8"/>
+    <pivotCache cacheId="14" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="286">
   <si>
     <t>Sources:</t>
   </si>
@@ -1079,25 +1079,29 @@
   <si>
     <t>PMCRS Policy Mandated Capacity Retrofit Schedule</t>
   </si>
+  <si>
+    <t>국내에는 CCS를 활용한 설비계획이 없음</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="181" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="182" formatCode="0.0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1105,21 +1109,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1127,7 +1131,7 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1151,7 +1155,7 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1172,7 +1176,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1185,14 +1189,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1293,7 +1297,7 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1322,6 +1326,20 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1652,7 +1670,7 @@
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1">
       <alignment wrapText="1"/>
@@ -1672,13 +1690,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1708,26 +1726,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="6" applyFont="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -1736,26 +1754,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="179" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1798,30 +1816,30 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="29" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="29" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="29" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="29" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="17" fillId="13" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="13" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="13" borderId="11" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="13" borderId="11" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1992,7 +2010,7 @@
     <xf numFmtId="1" fontId="24" fillId="12" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="7" applyFont="1" applyAlignment="1">
@@ -2011,17 +2029,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Comma 2 2" xfId="15" xr:uid="{E52FE600-546F-4F88-8BE6-396ADF4D3A73}"/>
     <cellStyle name="Comma 3" xfId="13" xr:uid="{8CAA9DCC-6534-4445-B4B7-CD4CD02EC2DD}"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Header: bottom row" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Normal 2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal 2 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
@@ -2029,6 +2046,8 @@
     <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Percent 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="Table title" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -2170,7 +2189,7 @@
     <cacheField name="Generator ID" numFmtId="49">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Net Summer Capacity (MW)" numFmtId="164">
+    <cacheField name="Net Summer Capacity (MW)" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.1" maxValue="1265"/>
     </cacheField>
     <cacheField name="Technology" numFmtId="0">
@@ -2213,7 +2232,7 @@
         <s v="(P) Planned for installation, but regulatory approvals not initiated"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Nameplate Capacity (MW)" numFmtId="164">
+    <cacheField name="Nameplate Capacity (MW)" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2" maxValue="2640"/>
     </cacheField>
   </cacheFields>
@@ -2267,7 +2286,7 @@
     <cacheField name="Generator ID" numFmtId="49">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Net Summer Capacity (MW)" numFmtId="164">
+    <cacheField name="Net Summer Capacity (MW)" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2" maxValue="2250"/>
     </cacheField>
     <cacheField name="Technology" numFmtId="0">
@@ -2304,7 +2323,7 @@
     <cacheField name="Status" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Nameplate Capacity (MW)" numFmtId="164">
+    <cacheField name="Nameplate Capacity (MW)" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2" maxValue="2640"/>
     </cacheField>
   </cacheFields>
@@ -2364,7 +2383,7 @@
     <cacheField name="Generator ID" numFmtId="49">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Net Summer Capacity (MW)" numFmtId="164">
+    <cacheField name="Net Summer Capacity (MW)" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.3" maxValue="1100"/>
     </cacheField>
     <cacheField name="Technology" numFmtId="0">
@@ -2408,7 +2427,7 @@
         <s v="(L) Regulatory approvals pending. Not under construction"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Nameplate Capacity (MW)" numFmtId="164">
+    <cacheField name="Nameplate Capacity (MW)" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.3" maxValue="1100"/>
     </cacheField>
   </cacheFields>
@@ -76182,7 +76201,195 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000002000000}" name="PivotTable3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000001000000}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A33:I52" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="15">
+    <pivotField axis="axisCol" showAll="0" sortType="ascending">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="15"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="17"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="177" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="13" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Net Summer Capacity (MW)" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="10" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000002000000}" name="PivotTable3" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A57:I76" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField axis="axisCol" showAll="0">
@@ -76206,7 +76413,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="22">
         <item h="1" x="16"/>
@@ -76236,7 +76443,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="10"/>
@@ -76338,8 +76545,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000000000000}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000000000000}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:I25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField axis="axisCol" showAll="0">
@@ -76372,7 +76579,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="21">
         <item x="16"/>
@@ -76412,7 +76619,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="10"/>
@@ -76513,200 +76720,12 @@
     <dataField name="Sum of Net Summer Capacity (MW)" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
             <x v="1"/>
           </reference>
-          <reference field="10" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0A00-000001000000}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A33:I52" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="15">
-    <pivotField axis="axisCol" showAll="0" sortType="ascending">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="15"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="17"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="18">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="13" hier="-1"/>
-    <pageField fld="4" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Net Summer Capacity (MW)" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="1">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
           <reference field="10" count="0"/>
         </references>
       </pivotArea>
@@ -77009,12 +77028,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="67.140625" customWidth="1"/>
+    <col min="2" max="2" width="67.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>284</v>
       </c>
@@ -77023,11 +77042,11 @@
       <c r="F1" s="45"/>
       <c r="G1" s="45"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F2" s="45"/>
       <c r="G2" s="45"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -77037,219 +77056,223 @@
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="45"/>
       <c r="G4" s="45"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>279</v>
       </c>
       <c r="F5" s="45"/>
       <c r="G5" s="45"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>2024</v>
       </c>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>280</v>
       </c>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>281</v>
       </c>
       <c r="F8" s="45"/>
       <c r="G8" s="45"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F9" s="45"/>
       <c r="G9" s="45"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="45"/>
       <c r="G10" s="45"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="45"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>195</v>
       </c>
       <c r="F12" s="45"/>
       <c r="G12" s="45"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="45"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F15" s="45"/>
       <c r="G15" s="45"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>282</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>283</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F18" s="45"/>
       <c r="G18" s="45"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F19" s="45"/>
       <c r="G19" s="45"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="150" t="s">
+        <v>285</v>
+      </c>
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F22" s="45"/>
       <c r="G22" s="45"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F24" s="45"/>
       <c r="G24" s="45"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F26" s="45"/>
       <c r="G26" s="45"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F28" s="45"/>
       <c r="G28" s="45"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F29" s="45"/>
       <c r="G29" s="45"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F30" s="45"/>
       <c r="G30" s="45"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F31" s="45"/>
       <c r="G31" s="45"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F32" s="45"/>
       <c r="G32" s="45"/>
     </row>
-    <row r="33" spans="6:7">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F33" s="45"/>
       <c r="G33" s="45"/>
     </row>
-    <row r="34" spans="6:7">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F34" s="45"/>
       <c r="G34" s="45"/>
     </row>
-    <row r="35" spans="6:7">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F35" s="45"/>
       <c r="G35" s="45"/>
     </row>
-    <row r="36" spans="6:7">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F36" s="45"/>
       <c r="G36" s="45"/>
     </row>
-    <row r="37" spans="6:7">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F37" s="45"/>
       <c r="G37" s="45"/>
     </row>
-    <row r="38" spans="6:7">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F38" s="45"/>
       <c r="G38" s="45"/>
     </row>
-    <row r="39" spans="6:7">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F39" s="45"/>
       <c r="G39" s="45"/>
     </row>
-    <row r="40" spans="6:7">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F40" s="45"/>
       <c r="G40" s="45"/>
     </row>
-    <row r="41" spans="6:7">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F41" s="45"/>
       <c r="G41" s="45"/>
     </row>
-    <row r="42" spans="6:7">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F42" s="45"/>
       <c r="G42" s="45"/>
     </row>
-    <row r="43" spans="6:7">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F43" s="45"/>
       <c r="G43" s="45"/>
     </row>
-    <row r="44" spans="6:7">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F44" s="45"/>
       <c r="G44" s="45"/>
     </row>
-    <row r="45" spans="6:7">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F45" s="45"/>
       <c r="G45" s="45"/>
     </row>
-    <row r="46" spans="6:7">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F46" s="45"/>
       <c r="G46" s="45"/>
     </row>
-    <row r="47" spans="6:7">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F47" s="45"/>
       <c r="G47" s="45"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
@@ -77258,13 +77281,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AH2837"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="4" t="s">
         <v>44</v>
       </c>
@@ -77362,8 +77385,8 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1" thickTop="1"/>
-    <row r="3" spans="1:34" ht="15" customHeight="1">
+    <row r="2" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
@@ -77375,7 +77398,7 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:34" ht="15" customHeight="1">
+    <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
         <v>47</v>
       </c>
@@ -77389,7 +77412,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1">
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="6" t="s">
         <v>50</v>
       </c>
@@ -77401,7 +77424,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="6" t="s">
         <v>52</v>
       </c>
@@ -77413,7 +77436,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:34" ht="15" customHeight="1">
+    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -77421,7 +77444,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="10" spans="1:34" ht="15" customHeight="1">
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>54</v>
       </c>
@@ -77432,7 +77455,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15" customHeight="1">
+    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>57</v>
       </c>
@@ -77440,7 +77463,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15" customHeight="1">
+    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -77477,7 +77500,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" thickBot="1">
+    <row r="13" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="5" t="s">
         <v>60</v>
       </c>
@@ -77578,18 +77601,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15" customHeight="1" thickTop="1"/>
-    <row r="15" spans="1:34" ht="15" customHeight="1">
+    <row r="14" spans="1:34" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15" customHeight="1">
+    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1">
+    <row r="17" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -77693,7 +77716,7 @@
         <v>-3.5593E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="15" customHeight="1">
+    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>66</v>
       </c>
@@ -77797,7 +77820,7 @@
         <v>-1.1639E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="15" customHeight="1">
+    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>68</v>
       </c>
@@ -77901,7 +77924,7 @@
         <v>2.2079999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="15" customHeight="1">
+    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>70</v>
       </c>
@@ -78005,7 +78028,7 @@
         <v>2.6945E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="15" customHeight="1">
+    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>72</v>
       </c>
@@ -78109,7 +78132,7 @@
         <v>-2.7585999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="15" customHeight="1">
+    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>74</v>
       </c>
@@ -78213,7 +78236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="15" customHeight="1">
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>76</v>
       </c>
@@ -78317,7 +78340,7 @@
         <v>5.9369999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="15" customHeight="1">
+    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>78</v>
       </c>
@@ -78421,7 +78444,7 @@
         <v>4.4720000000000003E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="15" customHeight="1">
+    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>80</v>
       </c>
@@ -78525,7 +78548,7 @@
         <v>2.9822000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="15" customHeight="1">
+    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>82</v>
       </c>
@@ -78629,7 +78652,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="15" customHeight="1">
+    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>85</v>
       </c>
@@ -78733,12 +78756,12 @@
         <v>1.5070999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="15" customHeight="1">
+    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="15" customHeight="1">
+    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>88</v>
       </c>
@@ -78842,7 +78865,7 @@
         <v>-1.9059999999999999E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="15" customHeight="1">
+    <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>90</v>
       </c>
@@ -78946,7 +78969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="14.85" customHeight="1">
+    <row r="31" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>92</v>
       </c>
@@ -79050,7 +79073,7 @@
         <v>-2.72E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="14.85" customHeight="1">
+    <row r="32" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>93</v>
       </c>
@@ -79154,7 +79177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="14.85" customHeight="1">
+    <row r="33" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>94</v>
       </c>
@@ -79258,7 +79281,7 @@
         <v>6.7999999999999999E-5</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="14.85" customHeight="1">
+    <row r="34" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>95</v>
       </c>
@@ -79362,12 +79385,12 @@
         <v>-3.3E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="14.85" customHeight="1">
+    <row r="36" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="14.85" customHeight="1">
+    <row r="37" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>97</v>
       </c>
@@ -79471,7 +79494,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="14.85" customHeight="1">
+    <row r="38" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>98</v>
       </c>
@@ -79575,7 +79598,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="14.85" customHeight="1">
+    <row r="39" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>99</v>
       </c>
@@ -79679,7 +79702,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="14.85" customHeight="1">
+    <row r="40" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>100</v>
       </c>
@@ -79783,7 +79806,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="14.85" customHeight="1">
+    <row r="41" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>101</v>
       </c>
@@ -79887,7 +79910,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="14.85" customHeight="1">
+    <row r="42" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>103</v>
       </c>
@@ -79991,7 +80014,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="14.85" customHeight="1">
+    <row r="43" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>104</v>
       </c>
@@ -80095,7 +80118,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="14.85" customHeight="1">
+    <row r="44" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>105</v>
       </c>
@@ -80199,7 +80222,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="14.85" customHeight="1">
+    <row r="45" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>106</v>
       </c>
@@ -80303,7 +80326,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="14.85" customHeight="1">
+    <row r="46" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>107</v>
       </c>
@@ -80407,7 +80430,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="14.85" customHeight="1">
+    <row r="47" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>109</v>
       </c>
@@ -80511,12 +80534,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="14.85" customHeight="1">
+    <row r="48" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="14.85" customHeight="1">
+    <row r="49" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>111</v>
       </c>
@@ -80620,7 +80643,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:34" ht="15" customHeight="1">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>112</v>
       </c>
@@ -80724,7 +80747,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:34" ht="15" customHeight="1">
+    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>113</v>
       </c>
@@ -80828,7 +80851,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:34" ht="15" customHeight="1">
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>114</v>
       </c>
@@ -80932,7 +80955,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>115</v>
       </c>
@@ -81036,7 +81059,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>116</v>
       </c>
@@ -81140,7 +81163,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:34" ht="15" customHeight="1">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>117</v>
       </c>
@@ -81244,7 +81267,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:34" ht="15" customHeight="1">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>118</v>
       </c>
@@ -81348,7 +81371,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="15" customHeight="1">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>119</v>
       </c>
@@ -81452,7 +81475,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:34" ht="15" customHeight="1">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>120</v>
       </c>
@@ -81556,7 +81579,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:34" ht="15" customHeight="1">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>121</v>
       </c>
@@ -81660,7 +81683,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:34" ht="15" customHeight="1">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>122</v>
       </c>
@@ -81764,12 +81787,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:34" ht="15" customHeight="1">
+    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1">
+    <row r="63" spans="1:34" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>125</v>
       </c>
@@ -81873,7 +81896,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:34" ht="15" customHeight="1">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>126</v>
       </c>
@@ -81977,7 +82000,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:34" ht="15" customHeight="1">
+    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>127</v>
       </c>
@@ -82081,7 +82104,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:34" ht="14.85" customHeight="1">
+    <row r="66" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>128</v>
       </c>
@@ -82185,7 +82208,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:34" ht="15" customHeight="1">
+    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>129</v>
       </c>
@@ -82289,7 +82312,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:34" ht="15" customHeight="1">
+    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>130</v>
       </c>
@@ -82393,7 +82416,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="15" customHeight="1">
+    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>131</v>
       </c>
@@ -82497,7 +82520,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:34" ht="15" customHeight="1">
+    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>132</v>
       </c>
@@ -82601,7 +82624,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:34" ht="15" customHeight="1">
+    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>133</v>
       </c>
@@ -82705,7 +82728,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="15" customHeight="1">
+    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>134</v>
       </c>
@@ -82809,7 +82832,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:34" ht="15" customHeight="1">
+    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>135</v>
       </c>
@@ -82913,12 +82936,12 @@
         <v>1.4742999999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:34" ht="15" customHeight="1">
+    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="77" spans="1:34" ht="15" customHeight="1">
+    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>138</v>
       </c>
@@ -83022,7 +83045,7 @@
         <v>-1.4040000000000001E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:34" ht="15" customHeight="1">
+    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
         <v>139</v>
       </c>
@@ -83126,7 +83149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:34" ht="14.85" customHeight="1">
+    <row r="79" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>141</v>
       </c>
@@ -83230,7 +83253,7 @@
         <v>2.2790999999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="15" customHeight="1">
+    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
         <v>143</v>
       </c>
@@ -83334,7 +83357,7 @@
         <v>5.0600000000000005E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="14.85" customHeight="1">
+    <row r="81" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>145</v>
       </c>
@@ -83438,7 +83461,7 @@
         <v>4.8174000000000002E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="15" customHeight="1">
+    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>146</v>
       </c>
@@ -83542,7 +83565,7 @@
         <v>2.5270000000000002E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:34" ht="15" customHeight="1">
+    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>148</v>
       </c>
@@ -83646,7 +83669,7 @@
         <v>3.9715E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:34" ht="15" customHeight="1">
+    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>149</v>
       </c>
@@ -83750,8 +83773,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:34" ht="15" customHeight="1" thickBot="1"/>
-    <row r="87" spans="1:34" ht="15" customHeight="1">
+    <row r="86" spans="1:34" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="144" t="s">
         <v>151</v>
       </c>
@@ -83788,127 +83811,127 @@
       <c r="AG87" s="145"/>
       <c r="AH87" s="23"/>
     </row>
-    <row r="88" spans="1:34" ht="15" customHeight="1">
+    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="24" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="89" spans="1:34" ht="15" customHeight="1">
+    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="24" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="1:34" ht="15" customHeight="1">
+    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="24" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:34" ht="15" customHeight="1">
+    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="24" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="92" spans="1:34" ht="14.85" customHeight="1">
+    <row r="92" spans="1:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="24" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="93" spans="1:34" ht="15" customHeight="1">
+    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="24" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:34" ht="15" customHeight="1">
+    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="24" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="95" spans="1:34" ht="15" customHeight="1">
+    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="24" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:34" ht="15" customHeight="1">
+    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="24" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="2:34" ht="15" customHeight="1">
+    <row r="97" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="24" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="98" spans="2:34" ht="15" customHeight="1">
+    <row r="98" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="24" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="2:34" ht="15" customHeight="1">
+    <row r="99" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="24" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="100" spans="2:34" ht="15" customHeight="1">
+    <row r="100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="24" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="101" spans="2:34" ht="14.85" customHeight="1">
+    <row r="101" spans="2:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="24" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="2:34" ht="14.85" customHeight="1">
+    <row r="102" spans="2:34" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="24" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="2:34" ht="15" customHeight="1">
+    <row r="103" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="24" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="104" spans="2:34" ht="15" customHeight="1">
+    <row r="104" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="24" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="105" spans="2:34" ht="15" customHeight="1">
+    <row r="105" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="24" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="106" spans="2:34" ht="15" customHeight="1">
+    <row r="106" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="24" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="107" spans="2:34" ht="15" customHeight="1">
+    <row r="107" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="24" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="108" spans="2:34" ht="15" customHeight="1">
+    <row r="108" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="24" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="109" spans="2:34" ht="15" customHeight="1">
+    <row r="109" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="24" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="2:34" ht="15" customHeight="1">
+    <row r="110" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="24" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="111" spans="2:34" ht="15" customHeight="1">
+    <row r="111" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="24" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="2:34" ht="15" customHeight="1">
+    <row r="112" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="143"/>
       <c r="C112" s="143"/>
       <c r="D112" s="143"/>
@@ -83943,7 +83966,7 @@
       <c r="AG112" s="143"/>
       <c r="AH112" s="143"/>
     </row>
-    <row r="308" spans="2:34" ht="15" customHeight="1">
+    <row r="308" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B308" s="143"/>
       <c r="C308" s="143"/>
       <c r="D308" s="143"/>
@@ -83978,7 +84001,7 @@
       <c r="AG308" s="143"/>
       <c r="AH308" s="143"/>
     </row>
-    <row r="511" spans="2:34" ht="15" customHeight="1">
+    <row r="511" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B511" s="143"/>
       <c r="C511" s="143"/>
       <c r="D511" s="143"/>
@@ -84013,7 +84036,7 @@
       <c r="AG511" s="143"/>
       <c r="AH511" s="143"/>
     </row>
-    <row r="712" spans="2:34" ht="15" customHeight="1">
+    <row r="712" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B712" s="143"/>
       <c r="C712" s="143"/>
       <c r="D712" s="143"/>
@@ -84048,7 +84071,7 @@
       <c r="AG712" s="143"/>
       <c r="AH712" s="143"/>
     </row>
-    <row r="887" spans="2:34" ht="15" customHeight="1">
+    <row r="887" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B887" s="143"/>
       <c r="C887" s="143"/>
       <c r="D887" s="143"/>
@@ -84083,7 +84106,7 @@
       <c r="AG887" s="143"/>
       <c r="AH887" s="143"/>
     </row>
-    <row r="1100" spans="2:34" ht="15" customHeight="1">
+    <row r="1100" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1100" s="143"/>
       <c r="C1100" s="143"/>
       <c r="D1100" s="143"/>
@@ -84118,7 +84141,7 @@
       <c r="AG1100" s="143"/>
       <c r="AH1100" s="143"/>
     </row>
-    <row r="1227" spans="2:34" ht="15" customHeight="1">
+    <row r="1227" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1227" s="143"/>
       <c r="C1227" s="143"/>
       <c r="D1227" s="143"/>
@@ -84153,7 +84176,7 @@
       <c r="AG1227" s="143"/>
       <c r="AH1227" s="143"/>
     </row>
-    <row r="1390" spans="2:34" ht="15" customHeight="1">
+    <row r="1390" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1390" s="143"/>
       <c r="C1390" s="143"/>
       <c r="D1390" s="143"/>
@@ -84188,7 +84211,7 @@
       <c r="AG1390" s="143"/>
       <c r="AH1390" s="143"/>
     </row>
-    <row r="1502" spans="2:34" ht="15" customHeight="1">
+    <row r="1502" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1502" s="143"/>
       <c r="C1502" s="143"/>
       <c r="D1502" s="143"/>
@@ -84223,7 +84246,7 @@
       <c r="AG1502" s="143"/>
       <c r="AH1502" s="143"/>
     </row>
-    <row r="1604" spans="2:34" ht="15" customHeight="1">
+    <row r="1604" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1604" s="143"/>
       <c r="C1604" s="143"/>
       <c r="D1604" s="143"/>
@@ -84258,7 +84281,7 @@
       <c r="AG1604" s="143"/>
       <c r="AH1604" s="143"/>
     </row>
-    <row r="1698" spans="2:34" ht="15" customHeight="1">
+    <row r="1698" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1698" s="143"/>
       <c r="C1698" s="143"/>
       <c r="D1698" s="143"/>
@@ -84293,7 +84316,7 @@
       <c r="AG1698" s="143"/>
       <c r="AH1698" s="143"/>
     </row>
-    <row r="1945" spans="2:34" ht="15" customHeight="1">
+    <row r="1945" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1945" s="143"/>
       <c r="C1945" s="143"/>
       <c r="D1945" s="143"/>
@@ -84328,7 +84351,7 @@
       <c r="AG1945" s="143"/>
       <c r="AH1945" s="143"/>
     </row>
-    <row r="2031" spans="2:34" ht="15" customHeight="1">
+    <row r="2031" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2031" s="143"/>
       <c r="C2031" s="143"/>
       <c r="D2031" s="143"/>
@@ -84363,7 +84386,7 @@
       <c r="AG2031" s="143"/>
       <c r="AH2031" s="143"/>
     </row>
-    <row r="2153" spans="2:34" ht="15" customHeight="1">
+    <row r="2153" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2153" s="143"/>
       <c r="C2153" s="143"/>
       <c r="D2153" s="143"/>
@@ -84398,7 +84421,7 @@
       <c r="AG2153" s="143"/>
       <c r="AH2153" s="143"/>
     </row>
-    <row r="2317" spans="2:34" ht="15" customHeight="1">
+    <row r="2317" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2317" s="143"/>
       <c r="C2317" s="143"/>
       <c r="D2317" s="143"/>
@@ -84433,7 +84456,7 @@
       <c r="AG2317" s="143"/>
       <c r="AH2317" s="143"/>
     </row>
-    <row r="2419" spans="2:34" ht="15" customHeight="1">
+    <row r="2419" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2419" s="143"/>
       <c r="C2419" s="143"/>
       <c r="D2419" s="143"/>
@@ -84468,7 +84491,7 @@
       <c r="AG2419" s="143"/>
       <c r="AH2419" s="143"/>
     </row>
-    <row r="2509" spans="2:34" ht="15" customHeight="1">
+    <row r="2509" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2509" s="143"/>
       <c r="C2509" s="143"/>
       <c r="D2509" s="143"/>
@@ -84503,7 +84526,7 @@
       <c r="AG2509" s="143"/>
       <c r="AH2509" s="143"/>
     </row>
-    <row r="2598" spans="2:34" ht="15" customHeight="1">
+    <row r="2598" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2598" s="143"/>
       <c r="C2598" s="143"/>
       <c r="D2598" s="143"/>
@@ -84538,7 +84561,7 @@
       <c r="AG2598" s="143"/>
       <c r="AH2598" s="143"/>
     </row>
-    <row r="2719" spans="2:34" ht="15" customHeight="1">
+    <row r="2719" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2719" s="143"/>
       <c r="C2719" s="143"/>
       <c r="D2719" s="143"/>
@@ -84573,7 +84596,7 @@
       <c r="AG2719" s="143"/>
       <c r="AH2719" s="143"/>
     </row>
-    <row r="2837" spans="2:34" ht="15" customHeight="1">
+    <row r="2837" spans="2:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2837" s="143"/>
       <c r="C2837" s="143"/>
       <c r="D2837" s="143"/>
@@ -84610,15 +84633,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B2598:AH2598"/>
-    <mergeCell ref="B2719:AH2719"/>
-    <mergeCell ref="B2837:AH2837"/>
-    <mergeCell ref="B1945:AH1945"/>
-    <mergeCell ref="B2031:AH2031"/>
-    <mergeCell ref="B2153:AH2153"/>
-    <mergeCell ref="B2317:AH2317"/>
-    <mergeCell ref="B2419:AH2419"/>
-    <mergeCell ref="B2509:AH2509"/>
     <mergeCell ref="B1698:AH1698"/>
     <mergeCell ref="B87:AG87"/>
     <mergeCell ref="B112:AH112"/>
@@ -84631,7 +84645,17 @@
     <mergeCell ref="B1390:AH1390"/>
     <mergeCell ref="B1502:AH1502"/>
     <mergeCell ref="B1604:AH1604"/>
+    <mergeCell ref="B2598:AH2598"/>
+    <mergeCell ref="B2719:AH2719"/>
+    <mergeCell ref="B2837:AH2837"/>
+    <mergeCell ref="B1945:AH1945"/>
+    <mergeCell ref="B2031:AH2031"/>
+    <mergeCell ref="B2153:AH2153"/>
+    <mergeCell ref="B2317:AH2317"/>
+    <mergeCell ref="B2419:AH2419"/>
+    <mergeCell ref="B2509:AH2509"/>
   </mergeCells>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
@@ -84640,13 +84664,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AH16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="47.5703125" style="38" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.625" style="38" customWidth="1"/>
+    <col min="8" max="8" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1">
+    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="12" t="s">
         <v>62</v>
       </c>
@@ -84775,12 +84799,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1">
+    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="15" customHeight="1">
+    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>64</v>
       </c>
@@ -84913,12 +84937,12 @@
       </c>
       <c r="AH3" s="19"/>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1">
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>125</v>
       </c>
@@ -85051,7 +85075,7 @@
       </c>
       <c r="AH6" s="19"/>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
         <v>176</v>
       </c>
@@ -85178,7 +85202,7 @@
       </c>
       <c r="AH8" s="28"/>
     </row>
-    <row r="9" spans="1:34" ht="30.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:34" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="29" t="s">
         <v>177</v>
       </c>
@@ -85304,7 +85328,7 @@
         <v>15.95382699999999</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" thickBot="1">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>178</v>
       </c>
@@ -85430,7 +85454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="30.75" customHeight="1" thickBot="1">
+    <row r="11" spans="1:34" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>178</v>
       </c>
@@ -85472,13 +85496,14 @@
       <c r="AF11" s="37"/>
       <c r="AG11" s="37"/>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="H15" s="39"/>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="H16" s="28"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -85487,26 +85512,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M77"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="37.28515625" customWidth="1"/>
+    <col min="13" max="13" width="37.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="43">
         <v>44197</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -85514,7 +85539,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>42</v>
       </c>
@@ -85522,12 +85547,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M4" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>183</v>
       </c>
@@ -85535,7 +85560,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>185</v>
       </c>
@@ -85564,7 +85589,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -85587,7 +85612,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -85613,7 +85638,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -85625,7 +85650,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -85643,7 +85668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -85667,7 +85692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -85690,7 +85715,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -85702,7 +85727,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
@@ -85715,7 +85740,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -85728,7 +85753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
@@ -85749,7 +85774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
@@ -85770,7 +85795,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
@@ -85799,7 +85824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
@@ -85816,7 +85841,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
@@ -85834,7 +85859,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>6</v>
       </c>
@@ -85848,7 +85873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
@@ -85874,7 +85899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -85887,7 +85912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
@@ -85900,7 +85925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>186</v>
       </c>
@@ -85929,15 +85954,15 @@
         <v>199.6</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M28" s="42"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="43">
         <v>44562</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>43</v>
       </c>
@@ -85945,7 +85970,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>42</v>
       </c>
@@ -85953,12 +85978,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M32" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>183</v>
       </c>
@@ -85966,7 +85991,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>185</v>
       </c>
@@ -85995,7 +86020,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
@@ -86022,7 +86047,7 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
@@ -86051,7 +86076,7 @@
         <v>hydro</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>15</v>
       </c>
@@ -86070,7 +86095,7 @@
         <v>geothermal</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>16</v>
       </c>
@@ -86089,7 +86114,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>10</v>
       </c>
@@ -86116,7 +86141,7 @@
         <v>natural gas combined cycle</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>11</v>
       </c>
@@ -86143,7 +86168,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>13</v>
       </c>
@@ -86164,7 +86189,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>9</v>
       </c>
@@ -86183,7 +86208,7 @@
         <v>natural gas steam turbine</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>20</v>
       </c>
@@ -86204,7 +86229,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>12</v>
       </c>
@@ -86229,7 +86254,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -86252,7 +86277,7 @@
         <v>offshore wind</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>7</v>
       </c>
@@ -86281,7 +86306,7 @@
         <v>onshore wind</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>19</v>
       </c>
@@ -86302,7 +86327,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>21</v>
       </c>
@@ -86323,7 +86348,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>6</v>
       </c>
@@ -86342,7 +86367,7 @@
         <v>petroleum</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>14</v>
       </c>
@@ -86373,7 +86398,7 @@
         <v>solar PV</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>22</v>
       </c>
@@ -86392,7 +86417,7 @@
         <v>solar thermal</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>186</v>
       </c>
@@ -86422,20 +86447,20 @@
       </c>
       <c r="M52" s="41"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M53" s="41"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>2023</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M56" s="41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>183</v>
       </c>
@@ -86443,7 +86468,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>185</v>
       </c>
@@ -86472,7 +86497,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>17</v>
       </c>
@@ -86499,7 +86524,7 @@
         <v>NA</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>8</v>
       </c>
@@ -86526,7 +86551,7 @@
         <v>hydro</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>15</v>
       </c>
@@ -86541,7 +86566,7 @@
         <v>geothermal</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>16</v>
       </c>
@@ -86556,7 +86581,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>10</v>
       </c>
@@ -86580,7 +86605,7 @@
         <v>natural gas combined cycle</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>11</v>
       </c>
@@ -86604,7 +86629,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>13</v>
       </c>
@@ -86622,7 +86647,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>9</v>
       </c>
@@ -86640,7 +86665,7 @@
         <v>natural gas steam turbine</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>20</v>
       </c>
@@ -86652,7 +86677,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>12</v>
       </c>
@@ -86673,7 +86698,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>23</v>
       </c>
@@ -86700,7 +86725,7 @@
         <v>offshore wind</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>7</v>
       </c>
@@ -86730,7 +86755,7 @@
         <v>onshore wind</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>19</v>
       </c>
@@ -86742,7 +86767,7 @@
         <v>natural gas peaker</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>21</v>
       </c>
@@ -86757,7 +86782,7 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>6</v>
       </c>
@@ -86769,7 +86794,7 @@
         <v>petroleum</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -86802,7 +86827,7 @@
         <v>solar PV</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>22</v>
       </c>
@@ -86814,7 +86839,7 @@
         <v>solar thermal</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>18</v>
       </c>
@@ -86826,13 +86851,14 @@
         <v>biomass</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M77" s="41" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -86840,14 +86866,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2FC87D5-F70B-4E40-8A44-F4753F5E6E9B}">
   <dimension ref="A1:AG158"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="65.28515625" style="99" customWidth="1"/>
+    <col min="1" max="1" width="65.25" style="99" customWidth="1"/>
     <col min="2" max="2" width="2" style="99" customWidth="1"/>
-    <col min="3" max="8" width="8.42578125" style="50" customWidth="1"/>
+    <col min="3" max="8" width="8.375" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="49"/>
       <c r="B1" s="49"/>
       <c r="C1" s="49"/>
@@ -86856,7 +86882,7 @@
       <c r="F1" s="49"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:14" ht="26.25">
+    <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="146" t="s">
         <v>196</v>
       </c>
@@ -86867,7 +86893,7 @@
       <c r="F2" s="146"/>
       <c r="G2" s="146"/>
     </row>
-    <row r="3" spans="1:14" ht="18">
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
@@ -86880,7 +86906,7 @@
       <c r="M3" s="147"/>
       <c r="N3" s="147"/>
     </row>
-    <row r="4" spans="1:14" ht="18">
+    <row r="4" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="148" t="s">
         <v>197</v>
       </c>
@@ -86891,7 +86917,7 @@
       <c r="F4" s="148"/>
       <c r="G4" s="148"/>
     </row>
-    <row r="5" spans="1:14" ht="18">
+    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
       <c r="B5" s="147"/>
       <c r="C5" s="147"/>
@@ -86900,7 +86926,7 @@
       <c r="F5" s="49"/>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="51"/>
       <c r="B6" s="51"/>
       <c r="C6" s="51" t="s">
@@ -86911,7 +86937,7 @@
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="149"/>
       <c r="B7" s="149"/>
       <c r="C7" s="149"/>
@@ -86920,7 +86946,7 @@
       <c r="F7" s="149"/>
       <c r="G7" s="149"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="53"/>
       <c r="B8" s="53"/>
       <c r="C8" s="53"/>
@@ -86929,7 +86955,7 @@
       <c r="F8" s="53"/>
       <c r="G8" s="53"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1">
+    <row r="9" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="54" t="s">
         <v>199</v>
       </c>
@@ -86938,7 +86964,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.75" thickBot="1">
+    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="56" t="s">
         <v>201</v>
       </c>
@@ -86966,7 +86992,7 @@
       </c>
       <c r="J10" s="60"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
         <v>202</v>
       </c>
@@ -86994,7 +87020,7 @@
       </c>
       <c r="J11" s="67"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="68" t="s">
         <v>203</v>
       </c>
@@ -87022,7 +87048,7 @@
       </c>
       <c r="J12" s="72"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="61" t="s">
         <v>204</v>
       </c>
@@ -87050,7 +87076,7 @@
       </c>
       <c r="J13" s="75"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="68" t="s">
         <v>205</v>
       </c>
@@ -87078,7 +87104,7 @@
       </c>
       <c r="J14" s="78"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1">
+    <row r="15" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="79" t="s">
         <v>206</v>
       </c>
@@ -87106,7 +87132,7 @@
       </c>
       <c r="J15" s="78"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1">
+    <row r="16" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="62"/>
       <c r="B16" s="62"/>
       <c r="C16" s="84"/>
@@ -87116,7 +87142,7 @@
       <c r="G16" s="84"/>
       <c r="H16" s="85"/>
     </row>
-    <row r="17" spans="1:11" ht="18.75" thickBot="1">
+    <row r="17" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="56" t="s">
         <v>207</v>
       </c>
@@ -87144,7 +87170,7 @@
       </c>
       <c r="J17" s="60"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1">
+    <row r="18" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="86" t="s">
         <v>208</v>
       </c>
@@ -87172,7 +87198,7 @@
       </c>
       <c r="J18" s="90"/>
     </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1">
+    <row r="19" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="62"/>
       <c r="B19" s="62"/>
       <c r="C19" s="91"/>
@@ -87182,7 +87208,7 @@
       <c r="G19" s="91"/>
       <c r="H19" s="92"/>
     </row>
-    <row r="20" spans="1:11" ht="18.75" thickBot="1">
+    <row r="20" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="56" t="s">
         <v>209</v>
       </c>
@@ -87210,7 +87236,7 @@
       </c>
       <c r="J20" s="60"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="61" t="s">
         <v>210</v>
       </c>
@@ -87238,7 +87264,7 @@
       </c>
       <c r="J21" s="95"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="68" t="s">
         <v>211</v>
       </c>
@@ -87252,7 +87278,7 @@
       <c r="I22" s="97"/>
       <c r="J22" s="95"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="98" t="s">
         <v>212</v>
       </c>
@@ -87279,7 +87305,7 @@
       </c>
       <c r="J23" s="95"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="100" t="s">
         <v>213</v>
       </c>
@@ -87307,7 +87333,7 @@
       </c>
       <c r="J24" s="95"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="61" t="s">
         <v>214</v>
       </c>
@@ -87321,7 +87347,7 @@
       <c r="I25" s="94"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="100" t="s">
         <v>215</v>
       </c>
@@ -87349,7 +87375,7 @@
       </c>
       <c r="J26" s="95"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="98" t="s">
         <v>216</v>
       </c>
@@ -87368,7 +87394,7 @@
       <c r="I27" s="94"/>
       <c r="J27" s="95"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="100" t="s">
         <v>217</v>
       </c>
@@ -87396,7 +87422,7 @@
       </c>
       <c r="J28" s="95"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="98" t="s">
         <v>218</v>
       </c>
@@ -87417,7 +87443,7 @@
       <c r="I29" s="94"/>
       <c r="J29" s="95"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="100" t="s">
         <v>219</v>
       </c>
@@ -87445,7 +87471,7 @@
       </c>
       <c r="J30" s="95"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1">
+    <row r="31" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="102" t="s">
         <v>220</v>
       </c>
@@ -87473,7 +87499,7 @@
       </c>
       <c r="J31" s="95"/>
     </row>
-    <row r="32" spans="1:11" ht="15.75" thickBot="1">
+    <row r="32" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="62"/>
       <c r="B32" s="62"/>
       <c r="C32" s="106"/>
@@ -87486,7 +87512,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="18.75" thickBot="1">
+    <row r="33" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="56" t="s">
         <v>221</v>
       </c>
@@ -87583,7 +87609,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="61" t="s">
         <v>222</v>
       </c>
@@ -87611,7 +87637,7 @@
       </c>
       <c r="J34" s="109"/>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="68" t="s">
         <v>223</v>
       </c>
@@ -87639,7 +87665,7 @@
       </c>
       <c r="J35" s="109"/>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="98" t="s">
         <v>224</v>
       </c>
@@ -87667,7 +87693,7 @@
       </c>
       <c r="J36" s="109"/>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="100" t="s">
         <v>225</v>
       </c>
@@ -87695,7 +87721,7 @@
       </c>
       <c r="J37" s="109"/>
     </row>
-    <row r="38" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="38" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="98" t="s">
         <v>226</v>
       </c>
@@ -87723,7 +87749,7 @@
       </c>
       <c r="J38" s="109"/>
     </row>
-    <row r="39" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="39" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="100" t="s">
         <v>227</v>
       </c>
@@ -87751,7 +87777,7 @@
       </c>
       <c r="J39" s="109"/>
     </row>
-    <row r="40" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="40" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A40" s="98" t="s">
         <v>228</v>
       </c>
@@ -87779,7 +87805,7 @@
       </c>
       <c r="J40" s="109"/>
     </row>
-    <row r="41" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="41" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="100" t="s">
         <v>229</v>
       </c>
@@ -87807,7 +87833,7 @@
       </c>
       <c r="J41" s="109"/>
     </row>
-    <row r="42" spans="1:33">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="61" t="s">
         <v>230</v>
       </c>
@@ -87834,7 +87860,7 @@
       </c>
       <c r="J42" s="109"/>
     </row>
-    <row r="43" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="43" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="100" t="s">
         <v>231</v>
       </c>
@@ -87862,7 +87888,7 @@
       </c>
       <c r="J43" s="109"/>
     </row>
-    <row r="44" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="44" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="98" t="s">
         <v>232</v>
       </c>
@@ -87890,7 +87916,7 @@
       </c>
       <c r="J44" s="109"/>
     </row>
-    <row r="45" spans="1:33" s="114" customFormat="1" ht="14.25">
+    <row r="45" spans="1:33" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A45" s="100" t="s">
         <v>233</v>
       </c>
@@ -88010,7 +88036,7 @@
         <v>0.7420077610000001</v>
       </c>
     </row>
-    <row r="46" spans="1:33">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="61" t="s">
         <v>234</v>
       </c>
@@ -88037,7 +88063,7 @@
       </c>
       <c r="J46" s="109"/>
     </row>
-    <row r="47" spans="1:33">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="68" t="s">
         <v>12</v>
       </c>
@@ -88065,7 +88091,7 @@
       </c>
       <c r="J47" s="109"/>
     </row>
-    <row r="48" spans="1:33">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="61" t="s">
         <v>235</v>
       </c>
@@ -88092,7 +88118,7 @@
       </c>
       <c r="J48" s="109"/>
     </row>
-    <row r="49" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="49" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="100" t="s">
         <v>236</v>
       </c>
@@ -88120,7 +88146,7 @@
       </c>
       <c r="J49" s="109"/>
     </row>
-    <row r="50" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="50" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="98" t="s">
         <v>237</v>
       </c>
@@ -88148,7 +88174,7 @@
       </c>
       <c r="J50" s="109"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="100" t="s">
         <v>238</v>
       </c>
@@ -88176,7 +88202,7 @@
       </c>
       <c r="J51" s="109"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="61" t="s">
         <v>239</v>
       </c>
@@ -88203,7 +88229,7 @@
       </c>
       <c r="J52" s="109"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="68" t="s">
         <v>240</v>
       </c>
@@ -88231,7 +88257,7 @@
       </c>
       <c r="J53" s="109"/>
     </row>
-    <row r="54" spans="1:10" ht="15.75" thickBot="1">
+    <row r="54" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="117" t="s">
         <v>186</v>
       </c>
@@ -88259,7 +88285,7 @@
       </c>
       <c r="J54" s="109"/>
     </row>
-    <row r="55" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="55" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="62"/>
       <c r="B55" s="62"/>
       <c r="C55" s="107"/>
@@ -88269,7 +88295,7 @@
       <c r="G55" s="107"/>
       <c r="H55" s="107"/>
     </row>
-    <row r="56" spans="1:10" ht="18.75" thickBot="1">
+    <row r="56" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="56" t="s">
         <v>241</v>
       </c>
@@ -88297,7 +88323,7 @@
       </c>
       <c r="J56" s="60"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="61" t="s">
         <v>222</v>
       </c>
@@ -88325,7 +88351,7 @@
       </c>
       <c r="J57" s="78"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="68" t="s">
         <v>223</v>
       </c>
@@ -88353,7 +88379,7 @@
       </c>
       <c r="J58" s="122"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="98" t="s">
         <v>224</v>
       </c>
@@ -88381,7 +88407,7 @@
       </c>
       <c r="J59" s="122"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="100" t="s">
         <v>225</v>
       </c>
@@ -88409,7 +88435,7 @@
       </c>
       <c r="J60" s="122"/>
     </row>
-    <row r="61" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="61" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A61" s="98" t="s">
         <v>226</v>
       </c>
@@ -88437,7 +88463,7 @@
       </c>
       <c r="J61" s="122"/>
     </row>
-    <row r="62" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="62" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A62" s="100" t="s">
         <v>227</v>
       </c>
@@ -88465,7 +88491,7 @@
       </c>
       <c r="J62" s="122"/>
     </row>
-    <row r="63" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="63" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A63" s="98" t="s">
         <v>228</v>
       </c>
@@ -88493,7 +88519,7 @@
       </c>
       <c r="J63" s="122"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="68" t="s">
         <v>230</v>
       </c>
@@ -88521,7 +88547,7 @@
       </c>
       <c r="J64" s="122"/>
     </row>
-    <row r="65" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="65" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A65" s="98" t="s">
         <v>231</v>
       </c>
@@ -88549,7 +88575,7 @@
       </c>
       <c r="J65" s="122"/>
     </row>
-    <row r="66" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="66" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="123" t="s">
         <v>232</v>
       </c>
@@ -88577,7 +88603,7 @@
       </c>
       <c r="J66" s="122"/>
     </row>
-    <row r="67" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="67" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A67" s="98" t="s">
         <v>233</v>
       </c>
@@ -88605,7 +88631,7 @@
       </c>
       <c r="J67" s="122"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="68" t="s">
         <v>234</v>
       </c>
@@ -88633,7 +88659,7 @@
       </c>
       <c r="J68" s="122"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="61" t="s">
         <v>12</v>
       </c>
@@ -88661,7 +88687,7 @@
       </c>
       <c r="J69" s="122"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="68" t="s">
         <v>235</v>
       </c>
@@ -88689,7 +88715,7 @@
       </c>
       <c r="J70" s="122"/>
     </row>
-    <row r="71" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="71" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A71" s="98" t="s">
         <v>236</v>
       </c>
@@ -88717,7 +88743,7 @@
       </c>
       <c r="J71" s="122"/>
     </row>
-    <row r="72" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="72" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A72" s="124" t="s">
         <v>237</v>
       </c>
@@ -88745,7 +88771,7 @@
       </c>
       <c r="J72" s="122"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="98" t="s">
         <v>238</v>
       </c>
@@ -88773,7 +88799,7 @@
       </c>
       <c r="J73" s="122"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="68" t="s">
         <v>240</v>
       </c>
@@ -88801,7 +88827,7 @@
       </c>
       <c r="J74" s="122"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1">
+    <row r="75" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="125" t="s">
         <v>186</v>
       </c>
@@ -88829,7 +88855,7 @@
       </c>
       <c r="J75" s="122"/>
     </row>
-    <row r="76" spans="1:10" ht="15.75" thickBot="1">
+    <row r="76" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="79"/>
       <c r="B76" s="80"/>
       <c r="C76" s="129"/>
@@ -88841,7 +88867,7 @@
       <c r="I76" s="129"/>
       <c r="J76" s="122"/>
     </row>
-    <row r="77" spans="1:10" ht="18.75" thickBot="1">
+    <row r="77" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="56" t="s">
         <v>242</v>
       </c>
@@ -88869,7 +88895,7 @@
       </c>
       <c r="J77" s="60"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="61" t="s">
         <v>222</v>
       </c>
@@ -88897,7 +88923,7 @@
       </c>
       <c r="J78" s="78"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="68" t="s">
         <v>223</v>
       </c>
@@ -88925,7 +88951,7 @@
       </c>
       <c r="J79" s="122"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="98" t="s">
         <v>224</v>
       </c>
@@ -88953,7 +88979,7 @@
       </c>
       <c r="J80" s="122"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="100" t="s">
         <v>225</v>
       </c>
@@ -88981,7 +89007,7 @@
       </c>
       <c r="J81" s="122"/>
     </row>
-    <row r="82" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="82" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A82" s="98" t="s">
         <v>226</v>
       </c>
@@ -89009,7 +89035,7 @@
       </c>
       <c r="J82" s="122"/>
     </row>
-    <row r="83" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="83" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A83" s="100" t="s">
         <v>227</v>
       </c>
@@ -89037,7 +89063,7 @@
       </c>
       <c r="J83" s="122"/>
     </row>
-    <row r="84" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="84" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="98" t="s">
         <v>228</v>
       </c>
@@ -89065,7 +89091,7 @@
       </c>
       <c r="J84" s="122"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="68" t="s">
         <v>230</v>
       </c>
@@ -89093,7 +89119,7 @@
       </c>
       <c r="J85" s="122"/>
     </row>
-    <row r="86" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="86" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A86" s="98" t="s">
         <v>231</v>
       </c>
@@ -89121,7 +89147,7 @@
       </c>
       <c r="J86" s="122"/>
     </row>
-    <row r="87" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="87" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A87" s="123" t="s">
         <v>232</v>
       </c>
@@ -89149,7 +89175,7 @@
       </c>
       <c r="J87" s="122"/>
     </row>
-    <row r="88" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="88" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A88" s="98" t="s">
         <v>233</v>
       </c>
@@ -89177,7 +89203,7 @@
       </c>
       <c r="J88" s="122"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="68" t="s">
         <v>234</v>
       </c>
@@ -89205,7 +89231,7 @@
       </c>
       <c r="J89" s="122"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="61" t="s">
         <v>12</v>
       </c>
@@ -89233,7 +89259,7 @@
       </c>
       <c r="J90" s="122"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="68" t="s">
         <v>235</v>
       </c>
@@ -89261,7 +89287,7 @@
       </c>
       <c r="J91" s="122"/>
     </row>
-    <row r="92" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="92" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A92" s="98" t="s">
         <v>236</v>
       </c>
@@ -89289,7 +89315,7 @@
       </c>
       <c r="J92" s="122"/>
     </row>
-    <row r="93" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="93" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A93" s="124" t="s">
         <v>237</v>
       </c>
@@ -89317,7 +89343,7 @@
       </c>
       <c r="J93" s="122"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="98" t="s">
         <v>238</v>
       </c>
@@ -89345,7 +89371,7 @@
       </c>
       <c r="J94" s="122"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="68" t="s">
         <v>240</v>
       </c>
@@ -89373,7 +89399,7 @@
       </c>
       <c r="J95" s="122"/>
     </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1">
+    <row r="96" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="125" t="s">
         <v>186</v>
       </c>
@@ -89401,7 +89427,7 @@
       </c>
       <c r="J96" s="122"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75" thickBot="1">
+    <row r="97" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="62"/>
       <c r="B97" s="62"/>
       <c r="C97" s="107"/>
@@ -89411,7 +89437,7 @@
       <c r="G97" s="107"/>
       <c r="H97" s="107"/>
     </row>
-    <row r="98" spans="1:10" ht="18.75" thickBot="1">
+    <row r="98" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="56" t="s">
         <v>243</v>
       </c>
@@ -89439,7 +89465,7 @@
       </c>
       <c r="J98" s="60"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="98" t="s">
         <v>244</v>
       </c>
@@ -89466,7 +89492,7 @@
       </c>
       <c r="J99" s="122"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="100" t="s">
         <v>245</v>
       </c>
@@ -89494,7 +89520,7 @@
       </c>
       <c r="J100" s="122"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="98" t="s">
         <v>246</v>
       </c>
@@ -89521,7 +89547,7 @@
       </c>
       <c r="J101" s="122"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="100" t="s">
         <v>247</v>
       </c>
@@ -89549,7 +89575,7 @@
       </c>
       <c r="J102" s="122"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="98" t="s">
         <v>248</v>
       </c>
@@ -89576,7 +89602,7 @@
       </c>
       <c r="J103" s="122"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="100" t="s">
         <v>249</v>
       </c>
@@ -89604,7 +89630,7 @@
       </c>
       <c r="J104" s="122"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="98" t="s">
         <v>250</v>
       </c>
@@ -89631,7 +89657,7 @@
       </c>
       <c r="J105" s="122"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="101" t="s">
         <v>251</v>
       </c>
@@ -89659,7 +89685,7 @@
       </c>
       <c r="J106" s="122"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="99" t="s">
         <v>252</v>
       </c>
@@ -89686,7 +89712,7 @@
       </c>
       <c r="J107" s="109"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="101" t="s">
         <v>253</v>
       </c>
@@ -89713,7 +89739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="99" t="s">
         <v>254</v>
       </c>
@@ -89740,7 +89766,7 @@
       </c>
       <c r="J109" s="60"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="101" t="s">
         <v>255</v>
       </c>
@@ -89768,7 +89794,7 @@
       </c>
       <c r="J110" s="109"/>
     </row>
-    <row r="111" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="111" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A111" s="99" t="s">
         <v>256</v>
       </c>
@@ -89796,7 +89822,7 @@
       </c>
       <c r="J111" s="109"/>
     </row>
-    <row r="112" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="112" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A112" s="101" t="s">
         <v>257</v>
       </c>
@@ -89824,7 +89850,7 @@
       </c>
       <c r="J112" s="109"/>
     </row>
-    <row r="113" spans="1:10" s="114" customFormat="1" ht="15.75" thickBot="1">
+    <row r="113" spans="1:10" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="125" t="s">
         <v>186</v>
       </c>
@@ -89852,7 +89878,7 @@
       </c>
       <c r="J113" s="109"/>
     </row>
-    <row r="114" spans="1:10" s="114" customFormat="1" ht="15.75" thickBot="1">
+    <row r="114" spans="1:10" s="114" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="99"/>
       <c r="B114" s="99"/>
       <c r="C114" s="107"/>
@@ -89864,7 +89890,7 @@
       <c r="I114"/>
       <c r="J114" s="109"/>
     </row>
-    <row r="115" spans="1:10" s="114" customFormat="1" ht="18.75" thickBot="1">
+    <row r="115" spans="1:10" s="114" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="56" t="s">
         <v>258</v>
       </c>
@@ -89892,7 +89918,7 @@
       </c>
       <c r="J115" s="109"/>
     </row>
-    <row r="116" spans="1:10" s="114" customFormat="1">
+    <row r="116" spans="1:10" s="114" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="61" t="s">
         <v>222</v>
       </c>
@@ -89920,7 +89946,7 @@
       </c>
       <c r="J116" s="109"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="68" t="s">
         <v>223</v>
       </c>
@@ -89948,7 +89974,7 @@
       </c>
       <c r="J117" s="133"/>
     </row>
-    <row r="118" spans="1:10" s="114" customFormat="1">
+    <row r="118" spans="1:10" s="114" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="98" t="s">
         <v>224</v>
       </c>
@@ -89976,7 +90002,7 @@
       </c>
       <c r="J118" s="109"/>
     </row>
-    <row r="119" spans="1:10" s="114" customFormat="1">
+    <row r="119" spans="1:10" s="114" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="100" t="s">
         <v>259</v>
       </c>
@@ -90004,7 +90030,7 @@
       </c>
       <c r="J119" s="109"/>
     </row>
-    <row r="120" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="120" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A120" s="98" t="s">
         <v>225</v>
       </c>
@@ -90032,7 +90058,7 @@
       </c>
       <c r="J120" s="109"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="100" t="s">
         <v>226</v>
       </c>
@@ -90060,7 +90086,7 @@
       </c>
       <c r="J121" s="109"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="98" t="s">
         <v>227</v>
       </c>
@@ -90087,7 +90113,7 @@
       </c>
       <c r="J122" s="109"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="100" t="s">
         <v>228</v>
       </c>
@@ -90115,7 +90141,7 @@
       </c>
       <c r="J123" s="109"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="98" t="s">
         <v>229</v>
       </c>
@@ -90142,7 +90168,7 @@
       </c>
       <c r="J124" s="109"/>
     </row>
-    <row r="125" spans="1:10" s="114" customFormat="1">
+    <row r="125" spans="1:10" s="114" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="68" t="s">
         <v>230</v>
       </c>
@@ -90170,7 +90196,7 @@
       </c>
       <c r="J125" s="109"/>
     </row>
-    <row r="126" spans="1:10" s="114" customFormat="1" ht="14.25">
+    <row r="126" spans="1:10" s="114" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A126" s="98" t="s">
         <v>260</v>
       </c>
@@ -90198,7 +90224,7 @@
       </c>
       <c r="J126" s="109"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="100" t="s">
         <v>232</v>
       </c>
@@ -90226,7 +90252,7 @@
       </c>
       <c r="J127" s="109"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="98" t="s">
         <v>233</v>
       </c>
@@ -90253,7 +90279,7 @@
       </c>
       <c r="J128" s="109"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="68" t="s">
         <v>234</v>
       </c>
@@ -90281,7 +90307,7 @@
       </c>
       <c r="J129" s="109"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="61" t="s">
         <v>12</v>
       </c>
@@ -90308,7 +90334,7 @@
       </c>
       <c r="J130" s="109"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="68" t="s">
         <v>235</v>
       </c>
@@ -90336,7 +90362,7 @@
       </c>
       <c r="J131" s="109"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="98" t="s">
         <v>236</v>
       </c>
@@ -90362,7 +90388,7 @@
         <v>1060.4055484272631</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="100" t="s">
         <v>237</v>
       </c>
@@ -90390,7 +90416,7 @@
       </c>
       <c r="J133" s="60"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="98" t="s">
         <v>238</v>
       </c>
@@ -90417,7 +90443,7 @@
       </c>
       <c r="J134" s="109"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="68" t="s">
         <v>239</v>
       </c>
@@ -90445,7 +90471,7 @@
       </c>
       <c r="J135" s="109"/>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="61" t="s">
         <v>240</v>
       </c>
@@ -90472,7 +90498,7 @@
       </c>
       <c r="J136" s="109"/>
     </row>
-    <row r="137" spans="1:10" ht="15.75" thickBot="1">
+    <row r="137" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="134" t="s">
         <v>186</v>
       </c>
@@ -90500,7 +90526,7 @@
       </c>
       <c r="J137" s="109"/>
     </row>
-    <row r="138" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
+    <row r="138" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="62"/>
       <c r="B138" s="62"/>
       <c r="C138" s="107"/>
@@ -90511,7 +90537,7 @@
       <c r="H138" s="107"/>
       <c r="J138" s="109"/>
     </row>
-    <row r="139" spans="1:10" ht="18.75" thickBot="1">
+    <row r="139" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="56" t="s">
         <v>261</v>
       </c>
@@ -90539,7 +90565,7 @@
       </c>
       <c r="J139" s="109"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="61" t="s">
         <v>262</v>
       </c>
@@ -90567,7 +90593,7 @@
       </c>
       <c r="J140" s="109"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="100" t="s">
         <v>263</v>
       </c>
@@ -90581,7 +90607,7 @@
       <c r="I141" s="111"/>
       <c r="J141" s="109"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="98" t="s">
         <v>264</v>
       </c>
@@ -90602,7 +90628,7 @@
       <c r="I142" s="108"/>
       <c r="J142" s="109"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="100" t="s">
         <v>265</v>
       </c>
@@ -90622,7 +90648,7 @@
       <c r="I143" s="111"/>
       <c r="J143" s="109"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="98" t="s">
         <v>266</v>
       </c>
@@ -90649,7 +90675,7 @@
       </c>
       <c r="J144" s="109"/>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="100" t="s">
         <v>267</v>
       </c>
@@ -90671,7 +90697,7 @@
       <c r="I145" s="111"/>
       <c r="J145" s="109"/>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="98" t="s">
         <v>268</v>
       </c>
@@ -90698,7 +90724,7 @@
       </c>
       <c r="J146" s="109"/>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="100" t="s">
         <v>269</v>
       </c>
@@ -90726,7 +90752,7 @@
       </c>
       <c r="J147" s="109"/>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="98" t="s">
         <v>264</v>
       </c>
@@ -90753,7 +90779,7 @@
       </c>
       <c r="J148" s="109"/>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="100" t="s">
         <v>266</v>
       </c>
@@ -90781,7 +90807,7 @@
       </c>
       <c r="J149" s="75"/>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="98" t="s">
         <v>268</v>
       </c>
@@ -90807,7 +90833,7 @@
         <v>39.010000009234588</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="68" t="s">
         <v>270</v>
       </c>
@@ -90834,7 +90860,7 @@
         <v>5.2116030849019062</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="98" t="s">
         <v>271</v>
       </c>
@@ -90854,7 +90880,7 @@
       <c r="H152" s="107"/>
       <c r="I152" s="108"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="100" t="s">
         <v>272</v>
       </c>
@@ -90881,7 +90907,7 @@
         <v>2.5205571355626204</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="98" t="s">
         <v>273</v>
       </c>
@@ -90907,7 +90933,7 @@
         <v>2.6910459493392862</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="100"/>
       <c r="B155" s="101"/>
       <c r="C155" s="110"/>
@@ -90918,7 +90944,7 @@
       <c r="H155" s="110"/>
       <c r="I155" s="111"/>
     </row>
-    <row r="156" spans="1:10" ht="15.75" thickBot="1">
+    <row r="156" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="79" t="s">
         <v>274</v>
       </c>
@@ -90945,7 +90971,7 @@
         <v>7.8382324901165461</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C157" s="73"/>
       <c r="D157" s="73"/>
       <c r="E157" s="73"/>
@@ -90954,7 +90980,7 @@
       <c r="H157" s="73"/>
       <c r="I157" s="73"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="99" t="s">
         <v>275</v>
       </c>
@@ -90967,6 +90993,7 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A7:G7"/>
   </mergeCells>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -90980,19 +91007,19 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="27" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.25" customWidth="1"/>
+    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="27" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>194</v>
       </c>
@@ -91090,7 +91117,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="47" t="s">
         <v>26</v>
       </c>
@@ -91188,7 +91215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="47" t="s">
         <v>31</v>
       </c>
@@ -91286,7 +91313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="47" t="s">
         <v>25</v>
       </c>
@@ -91384,7 +91411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="47" t="s">
         <v>38</v>
       </c>
@@ -91482,7 +91509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>27</v>
       </c>
@@ -91580,7 +91607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" s="47" t="s">
         <v>35</v>
       </c>
@@ -91678,7 +91705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>39</v>
       </c>
@@ -91776,7 +91803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="47" t="s">
         <v>34</v>
       </c>
@@ -91874,7 +91901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>24</v>
       </c>
@@ -91972,7 +91999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>30</v>
       </c>
@@ -92070,7 +92097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>28</v>
       </c>
@@ -92168,7 +92195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>29</v>
       </c>
@@ -92266,7 +92293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>32</v>
       </c>
@@ -92364,7 +92391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>36</v>
       </c>
@@ -92462,7 +92489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
         <v>40</v>
       </c>
@@ -92560,7 +92587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
         <v>41</v>
       </c>
@@ -92658,7 +92685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
         <v>33</v>
       </c>
@@ -92756,7 +92783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>187</v>
       </c>
@@ -92789,39 +92816,30 @@
         <v>0</v>
       </c>
       <c r="K19" s="141">
-        <f>MAX((Summary!L45-Summary!K45)*1000,0)</f>
-        <v>484.44984249999834</v>
+        <v>0</v>
       </c>
       <c r="L19" s="141">
-        <f>MAX((Summary!M45-Summary!L45)*1000,0)</f>
-        <v>484.44984249999834</v>
+        <v>0</v>
       </c>
       <c r="M19" s="141">
-        <f>MAX((Summary!N45-Summary!M45)*1000,0)</f>
-        <v>3641.6150863997245</v>
+        <v>0</v>
       </c>
       <c r="N19" s="141">
-        <f>MAX((Summary!O45-Summary!N45)*1000,0)</f>
-        <v>3641.6150863997245</v>
+        <v>0</v>
       </c>
       <c r="O19" s="141">
-        <f>MAX((Summary!P45-Summary!O45)*1000,0)</f>
-        <v>3641.6150863997245</v>
+        <v>0</v>
       </c>
       <c r="P19" s="141">
-        <f>MAX((Summary!Q45-Summary!P45)*1000,0)</f>
-        <v>3641.615086400634</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="141">
-        <f>MAX((Summary!R45-Summary!Q45)*1000,0)</f>
-        <v>3641.6150863997245</v>
+        <v>0</v>
       </c>
       <c r="R19" s="141">
-        <f>MAX((Summary!S45-Summary!R45)*1000,0)</f>
         <v>0</v>
       </c>
       <c r="S19" s="141">
-        <f>MAX((Summary!T45-Summary!S45)*1000,0)</f>
         <v>0</v>
       </c>
       <c r="T19" s="141">
@@ -92877,7 +92895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>188</v>
       </c>
@@ -92975,7 +92993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>189</v>
       </c>
@@ -93073,7 +93091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>190</v>
       </c>
@@ -93171,7 +93189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>191</v>
       </c>
@@ -93269,7 +93287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="48" t="s">
         <v>192</v>
       </c>
@@ -93367,7 +93385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" s="48" t="s">
         <v>193</v>
       </c>
@@ -93466,6 +93484,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -93630,13 +93649,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65B90A8E-4DEA-49F5-8E72-AD5B447E2775}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A9688E5-71F1-4E00-9824-5153C45FD525}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354982D4-7117-41F6-BFD4-E9FB39A896C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84C87D65-72F0-4D61-81F1-832087B6BA9A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74DD6AA2-F9C2-4570-B40A-EAF66B51B0D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A9EE36-6971-4BF1-BE7F-ED60B0A2CD15}"/>
 </file>